--- a/artfynd/A 46143-2024 artfynd.xlsx
+++ b/artfynd/A 46143-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>120864197</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46143-2024 artfynd.xlsx
+++ b/artfynd/A 46143-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119039845</v>
+        <v>119719071</v>
       </c>
       <c r="B2" t="n">
-        <v>4764</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>skog V Spångmyran, Ultervik, Vb</t>
+          <t>Degersjön S, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768539</v>
+        <v>768546</v>
       </c>
       <c r="R2" t="n">
-        <v>7084469</v>
+        <v>7084518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,83 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120864197</v>
+        <v>69361438</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spångmyrtjärn, Vb</t>
+          <t>Spångmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768506</v>
+        <v>768479</v>
       </c>
       <c r="R3" t="n">
-        <v>7084491</v>
+        <v>7084688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2018-02-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2018-02-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +857,455 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119719117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Degersjön S, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>768475</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7084691</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120122319</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spångmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>768524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7084565</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olov Tranberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119039845</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>skog V Spångmyran, Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768539</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7084469</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120864197</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spångmyrtjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>768506</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7084491</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Isac Enetjärn</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Isac Enetjärn</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46143-2024 artfynd.xlsx
+++ b/artfynd/A 46143-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69361438</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120122319</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119039845</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120864197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,8 +1336,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>